--- a/data/trans_orig/P33B2_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P33B2_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia con la que se despierta durante la noche y tiene dificultad en volver a dormirse en 2023</t>
+          <t>Población según la frecuencia con la que se despierta durante la noche y tiene dificultad en volver a dormirse en 2023 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4531</t>
+          <t>4334</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>479</t>
+          <t>495</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4312</t>
+          <t>4592</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>772</t>
+          <t>979</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6215</t>
+          <t>6284</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23813</t>
+          <t>23836</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>48149</t>
+          <t>46011</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29564</t>
+          <t>28910</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>45701</t>
+          <t>45217</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>57923</t>
+          <t>57493</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>86055</t>
+          <t>87119</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,49%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13544</t>
+          <t>12826</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>30732</t>
+          <t>30486</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>30208</t>
+          <t>30061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>48362</t>
+          <t>48909</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>47654</t>
+          <t>47145</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>72688</t>
+          <t>73279</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,19%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>240377</t>
+          <t>241424</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>269341</t>
+          <t>268857</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>77,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>200065</t>
+          <t>200159</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>224551</t>
+          <t>224791</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>69,07%</t>
+          <t>69,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>449936</t>
+          <t>449167</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>486763</t>
+          <t>488132</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>74,85%</t>
+          <t>74,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>80,98%</t>
+          <t>81,21%</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>39192</t>
+          <t>36226</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>24514</t>
+          <t>25246</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>44139</t>
+          <t>43825</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>40037</t>
+          <t>40242</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>71440</t>
+          <t>71982</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,97%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19021</t>
+          <t>19629</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44522</t>
+          <t>43746</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35564</t>
+          <t>35565</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>58396</t>
+          <t>56453</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>60335</t>
+          <t>60213</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>92665</t>
+          <t>93692</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,07%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>65049</t>
+          <t>65069</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>106268</t>
+          <t>104789</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>96592</t>
+          <t>96831</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>127953</t>
+          <t>127442</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>171076</t>
+          <t>169674</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>221854</t>
+          <t>222054</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,49%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>359888</t>
+          <t>358623</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>408366</t>
+          <t>406934</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>69,18%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>78,5%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>305434</t>
+          <t>305492</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>345534</t>
+          <t>343741</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>59,31%</t>
+          <t>59,32%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>67,1%</t>
+          <t>66,75%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>677882</t>
+          <t>676363</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>742005</t>
+          <t>740041</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>65,6%</t>
+          <t>65,45%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>71,81%</t>
+          <t>71,62%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11241</t>
+          <t>11040</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>25675</t>
+          <t>25496</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>23977</t>
+          <t>23466</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>42362</t>
+          <t>41543</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>38794</t>
+          <t>38382</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>60455</t>
+          <t>61973</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,32%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16356</t>
+          <t>15719</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>33856</t>
+          <t>33355</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>37014</t>
+          <t>38267</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>58601</t>
+          <t>59404</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>58622</t>
+          <t>58356</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>85900</t>
+          <t>85049</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,8%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>34807</t>
+          <t>33640</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>56854</t>
+          <t>56199</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>61734</t>
+          <t>61403</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>87100</t>
+          <t>85405</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>101428</t>
+          <t>103634</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>136613</t>
+          <t>137242</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,65%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>213337</t>
+          <t>214684</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>243385</t>
+          <t>244405</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>67,5%</t>
+          <t>67,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,01%</t>
+          <t>77,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>178492</t>
+          <t>181275</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>210827</t>
+          <t>212444</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>52,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>60,47%</t>
+          <t>60,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>405020</t>
+          <t>401192</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>448239</t>
+          <t>447258</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>60,93%</t>
+          <t>60,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>67,44%</t>
+          <t>67,29%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12732</t>
+          <t>11938</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>32195</t>
+          <t>31375</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>20270</t>
+          <t>21376</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>48878</t>
+          <t>48373</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>37902</t>
+          <t>38457</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>72073</t>
+          <t>71252</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,04%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>20395</t>
+          <t>20961</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>45679</t>
+          <t>46719</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>26587</t>
+          <t>26404</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>59107</t>
+          <t>59282</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>51833</t>
+          <t>50465</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>97752</t>
+          <t>95343</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,1%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>31731</t>
+          <t>31658</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>60458</t>
+          <t>60485</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>58906</t>
+          <t>52925</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>119672</t>
+          <t>120579</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>101587</t>
+          <t>98811</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>164621</t>
+          <t>162811</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,65%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>196981</t>
+          <t>195794</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>235203</t>
+          <t>235166</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>63,02%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>75,24%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>260496</t>
+          <t>258213</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>369608</t>
+          <t>375344</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>54,76%</t>
+          <t>54,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>78,9%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>476513</t>
+          <t>480131</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>588701</t>
+          <t>597729</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>60,45%</t>
+          <t>60,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>74,68%</t>
+          <t>75,83%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2276</t>
+          <t>2066</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>9435</t>
+          <t>9164</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6312</t>
+          <t>6360</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>13965</t>
+          <t>14105</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>9966</t>
+          <t>10068</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>19887</t>
+          <t>19398</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5801</t>
+          <t>5866</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>15551</t>
+          <t>15531</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>9669</t>
+          <t>9701</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>19542</t>
+          <t>20105</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>17706</t>
+          <t>17569</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>31181</t>
+          <t>31174</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,05%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>119206</t>
+          <t>116270</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>140078</t>
+          <t>139445</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>66,69%</t>
+          <t>65,05%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>78,37%</t>
+          <t>78,01%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>144025</t>
+          <t>142357</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>162721</t>
+          <t>162565</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>69,15%</t>
+          <t>68,35%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>78,13%</t>
+          <t>78,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>269172</t>
+          <t>268500</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>297791</t>
+          <t>295690</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>69,55%</t>
+          <t>69,38%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>76,4%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>25153</t>
+          <t>25016</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>45531</t>
+          <t>46579</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>22777</t>
+          <t>23234</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>40632</t>
+          <t>41061</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>52572</t>
+          <t>53950</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>78665</t>
+          <t>79988</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,67%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>10049</t>
+          <t>10259</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>24898</t>
+          <t>24932</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>17146</t>
+          <t>16802</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>31339</t>
+          <t>30483</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>30475</t>
+          <t>30879</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>50098</t>
+          <t>49582</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,41%</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>18037</t>
+          <t>17856</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>33778</t>
+          <t>34049</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>39643</t>
+          <t>39079</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>57940</t>
+          <t>57201</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>62093</t>
+          <t>61505</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>86472</t>
+          <t>85811</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,29%</t>
         </is>
       </c>
     </row>
@@ -3801,12 +3801,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>29953</t>
+          <t>29619</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>48118</t>
+          <t>48761</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>34940</t>
+          <t>34322</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>51846</t>
+          <t>52093</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>68388</t>
+          <t>68869</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>94228</t>
+          <t>94238</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -3914,12 +3914,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>176887</t>
+          <t>175385</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>203250</t>
+          <t>201696</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3929,12 +3929,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>65,6%</t>
+          <t>65,05%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>75,38%</t>
+          <t>74,8%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>129725</t>
+          <t>129668</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>155758</t>
+          <t>154984</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>50,47%</t>
+          <t>50,44%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>60,59%</t>
+          <t>60,29%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>313252</t>
+          <t>315141</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>349875</t>
+          <t>350367</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>59,83%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>66,43%</t>
+          <t>66,52%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>23350</t>
+          <t>23626</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>46556</t>
+          <t>45331</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>30522</t>
+          <t>28358</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>89523</t>
+          <t>89753</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>57810</t>
+          <t>58984</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>121568</t>
+          <t>119730</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,13%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>35604</t>
+          <t>34555</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>59953</t>
+          <t>61942</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>53716</t>
+          <t>49901</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>134697</t>
+          <t>135651</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>91818</t>
+          <t>90593</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>174524</t>
+          <t>177136</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>12,03%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>115993</t>
+          <t>118234</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>163550</t>
+          <t>160977</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>210025</t>
+          <t>207656</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>582745</t>
+          <t>609789</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>68,62%</t>
+          <t>71,8%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>337669</t>
+          <t>342694</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>884337</t>
+          <t>810989</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>60,06%</t>
+          <t>55,08%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>380096</t>
+          <t>380408</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>434644</t>
+          <t>431924</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>60,99%</t>
+          <t>61,04%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>69,74%</t>
+          <t>69,3%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>171366</t>
+          <t>155902</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>427333</t>
+          <t>430417</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>50,32%</t>
+          <t>50,68%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>437290</t>
+          <t>490966</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>857330</t>
+          <t>853022</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>33,34%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>58,22%</t>
+          <t>57,93%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>40875</t>
+          <t>43686</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>135872</t>
+          <t>137108</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>118938</t>
+          <t>118387</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>149621</t>
+          <t>151482</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>141678</t>
+          <t>139023</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>280334</t>
+          <t>278996</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,97%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>17837</t>
+          <t>22463</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>68820</t>
+          <t>69828</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>70524</t>
+          <t>69439</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>97741</t>
+          <t>96249</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>80591</t>
+          <t>80554</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>161311</t>
+          <t>160653</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,77%</t>
         </is>
       </c>
     </row>
@@ -4939,12 +4939,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>37515</t>
+          <t>36658</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>127988</t>
+          <t>128919</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>97411</t>
+          <t>96791</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>129287</t>
+          <t>128382</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>126307</t>
+          <t>127288</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>244805</t>
+          <t>246831</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>15,01%</t>
         </is>
       </c>
     </row>
@@ -5052,12 +5052,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>605948</t>
+          <t>603072</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>824312</t>
+          <t>826048</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>65,25%</t>
+          <t>64,94%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>362450</t>
+          <t>362522</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>410019</t>
+          <t>409646</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>50,66%</t>
+          <t>50,67%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>57,31%</t>
+          <t>57,26%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>973151</t>
+          <t>972753</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1296852</t>
+          <t>1296121</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>59,19%</t>
+          <t>59,17%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>78,88%</t>
+          <t>78,83%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>164450</t>
+          <t>164739</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>240846</t>
+          <t>241932</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>272533</t>
+          <t>263960</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>368388</t>
+          <t>369815</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>464362</t>
+          <t>471457</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>591541</t>
+          <t>596950</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,39%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>191402</t>
+          <t>193285</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>282418</t>
+          <t>279149</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>338174</t>
+          <t>342095</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>458051</t>
+          <t>464038</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>577240</t>
+          <t>585885</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>722211</t>
+          <t>726489</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,21%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>446576</t>
+          <t>455661</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>648589</t>
+          <t>656590</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>817813</t>
+          <t>818927</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>1480652</t>
+          <t>1552193</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>42,42%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>1365154</t>
+          <t>1375464</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>2119739</t>
+          <t>2165804</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>30,43%</t>
         </is>
       </c>
     </row>
@@ -5621,12 +5621,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>2316502</t>
+          <t>2315878</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>2669232</t>
+          <t>2660483</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5636,12 +5636,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>66,97%</t>
+          <t>66,96%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>77,17%</t>
+          <t>76,92%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>1552200</t>
+          <t>1531210</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>2061828</t>
+          <t>2059356</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>56,35%</t>
+          <t>56,28%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>3943748</t>
+          <t>3957080</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>4594389</t>
+          <t>4592467</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>55,59%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>64,52%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P33B2_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P33B2_2023-Provincia-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>838</t>
+          <t>805</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4334</t>
+          <t>4400</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1711</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>502</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4592</t>
+          <t>5085</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2549</t>
+          <t>2813</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -805,22 +805,22 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6284</t>
+          <t>6431</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>33706</t>
+          <t>33467</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23836</t>
+          <t>24045</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>46011</t>
+          <t>45021</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>36854</t>
+          <t>40150</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28910</t>
+          <t>31805</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>45217</t>
+          <t>48177</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>70561</t>
+          <t>73617</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>57493</t>
+          <t>61620</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>87119</t>
+          <t>88159</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>13,89%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>20384</t>
+          <t>26171</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12826</t>
+          <t>18452</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>30486</t>
+          <t>36672</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>38694</t>
+          <t>45171</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>30061</t>
+          <t>34976</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>48909</t>
+          <t>56783</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>59078</t>
+          <t>71342</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>47145</t>
+          <t>58449</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>73279</t>
+          <t>85165</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>13,41%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>256514</t>
+          <t>258402</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>241424</t>
+          <t>244735</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>268857</t>
+          <t>271043</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>82,36%</t>
+          <t>81,04%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>77,52%</t>
+          <t>76,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>212376</t>
+          <t>228732</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>200159</t>
+          <t>215617</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>224791</t>
+          <t>242406</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>73,33%</t>
+          <t>72,37%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>69,11%</t>
+          <t>68,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>77,61%</t>
+          <t>76,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>468890</t>
+          <t>487134</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>449167</t>
+          <t>469075</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>488132</t>
+          <t>505501</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>78,01%</t>
+          <t>76,73%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>74,73%</t>
+          <t>73,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>81,21%</t>
+          <t>79,62%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>20472</t>
+          <t>21248</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11823</t>
+          <t>11887</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>36226</t>
+          <t>34958</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>33359</t>
+          <t>34390</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>25246</t>
+          <t>24823</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>43825</t>
+          <t>44401</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>53831</t>
+          <t>55638</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>40242</t>
+          <t>42278</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>71982</t>
+          <t>73563</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,83%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>29568</t>
+          <t>29576</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19629</t>
+          <t>19232</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>43746</t>
+          <t>45148</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>44975</t>
+          <t>47667</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35565</t>
+          <t>38552</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>56453</t>
+          <t>60675</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>74542</t>
+          <t>77244</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>60213</t>
+          <t>61305</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>93692</t>
+          <t>95180</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,84%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>84666</t>
+          <t>87133</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>65069</t>
+          <t>69315</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>104789</t>
+          <t>109797</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>111254</t>
+          <t>117979</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>96831</t>
+          <t>101151</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>127442</t>
+          <t>134438</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>195920</t>
+          <t>205113</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>169674</t>
+          <t>178967</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>222054</t>
+          <t>230574</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,41%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>383684</t>
+          <t>392689</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>358623</t>
+          <t>366886</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>406934</t>
+          <t>415466</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>74,0%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>69,14%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>78,5%</t>
+          <t>78,29%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>325382</t>
+          <t>346458</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>305492</t>
+          <t>325353</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>343741</t>
+          <t>366547</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>63,18%</t>
+          <t>63,4%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>59,32%</t>
+          <t>59,53%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>66,75%</t>
+          <t>67,07%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,17 +1703,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>709066</t>
+          <t>739147</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>676363</t>
+          <t>703595</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>740041</t>
+          <t>771478</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,7 +1723,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>65,45%</t>
+          <t>65,32%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>17624</t>
+          <t>17375</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11040</t>
+          <t>11216</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>25496</t>
+          <t>25707</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>31271</t>
+          <t>33141</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>23466</t>
+          <t>24989</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>41543</t>
+          <t>42437</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>48894</t>
+          <t>50516</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>38382</t>
+          <t>40041</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>61973</t>
+          <t>63286</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,42%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>23517</t>
+          <t>24719</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15719</t>
+          <t>17248</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>33355</t>
+          <t>34590</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>47631</t>
+          <t>48237</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>38267</t>
+          <t>37916</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>59404</t>
+          <t>59684</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>71148</t>
+          <t>72955</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>58356</t>
+          <t>59972</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>85049</t>
+          <t>87267</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,99%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>44852</t>
+          <t>45697</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>33640</t>
+          <t>36298</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>56199</t>
+          <t>59244</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>73538</t>
+          <t>74935</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>61403</t>
+          <t>62571</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>85405</t>
+          <t>87993</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>118389</t>
+          <t>120632</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>103634</t>
+          <t>104518</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>137242</t>
+          <t>137605</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,48%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>230057</t>
+          <t>228203</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>214684</t>
+          <t>213313</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>244405</t>
+          <t>242542</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>72,79%</t>
+          <t>72,22%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>67,93%</t>
+          <t>67,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>76,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>196186</t>
+          <t>199529</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>181275</t>
+          <t>184054</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>212444</t>
+          <t>217871</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>56,27%</t>
+          <t>56,07%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>52,0%</t>
+          <t>51,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>60,94%</t>
+          <t>61,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>426243</t>
+          <t>427732</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>401192</t>
+          <t>408130</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>447258</t>
+          <t>450945</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>64,13%</t>
+          <t>63,67%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>60,36%</t>
+          <t>60,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>67,29%</t>
+          <t>67,12%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>348625</t>
+          <t>355842</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>348625</t>
+          <t>355842</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>348625</t>
+          <t>355842</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>664675</t>
+          <t>671836</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>664675</t>
+          <t>671836</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>664675</t>
+          <t>671836</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>20253</t>
+          <t>23338</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11938</t>
+          <t>13659</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>31375</t>
+          <t>35718</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>33827</t>
+          <t>37792</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21376</t>
+          <t>28732</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>48373</t>
+          <t>52211</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>54079</t>
+          <t>61130</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>38457</t>
+          <t>47451</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>71252</t>
+          <t>79543</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>10,0%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>31224</t>
+          <t>35945</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>20961</t>
+          <t>23562</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>46719</t>
+          <t>50843</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>43643</t>
+          <t>49329</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>26404</t>
+          <t>38969</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>59282</t>
+          <t>64173</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>74867</t>
+          <t>85274</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>50465</t>
+          <t>69292</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>95343</t>
+          <t>107692</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>13,54%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>43866</t>
+          <t>48921</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>31658</t>
+          <t>36008</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>60485</t>
+          <t>66558</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>93055</t>
+          <t>99648</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>52925</t>
+          <t>84582</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>120579</t>
+          <t>114924</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>136920</t>
+          <t>148569</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>98811</t>
+          <t>127995</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>162811</t>
+          <t>170787</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>21,48%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>217214</t>
+          <t>264941</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>195794</t>
+          <t>241907</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>235166</t>
+          <t>286890</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>69,5%</t>
+          <t>71,0%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>62,64%</t>
+          <t>64,83%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>75,24%</t>
+          <t>76,88%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>305193</t>
+          <t>235192</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>258213</t>
+          <t>215032</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>375344</t>
+          <t>254495</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>64,15%</t>
+          <t>55,74%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>54,28%</t>
+          <t>50,96%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>78,9%</t>
+          <t>60,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>522407</t>
+          <t>500134</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>480131</t>
+          <t>472474</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>597729</t>
+          <t>527422</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>66,27%</t>
+          <t>62,9%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>60,91%</t>
+          <t>59,42%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>75,83%</t>
+          <t>66,33%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>4706</t>
+          <t>5084</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2066</t>
+          <t>2262</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>9164</t>
+          <t>9753</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>9674</t>
+          <t>10512</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6360</t>
+          <t>7049</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>14105</t>
+          <t>15454</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>14380</t>
+          <t>15597</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>10068</t>
+          <t>11094</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>19398</t>
+          <t>21333</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>9618</t>
+          <t>10185</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5866</t>
+          <t>6164</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>15531</t>
+          <t>15943</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>13885</t>
+          <t>13962</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>9701</t>
+          <t>9861</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>20105</t>
+          <t>18553</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>23503</t>
+          <t>24147</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>17569</t>
+          <t>17568</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>31174</t>
+          <t>31115</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,19%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>130283</t>
+          <t>146642</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>116270</t>
+          <t>133858</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>139445</t>
+          <t>157562</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>72,89%</t>
+          <t>71,3%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>65,05%</t>
+          <t>65,09%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>78,01%</t>
+          <t>76,61%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>153630</t>
+          <t>165422</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>142357</t>
+          <t>153968</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>162565</t>
+          <t>175491</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>72,93%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>68,35%</t>
+          <t>67,88%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>78,05%</t>
+          <t>77,37%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>283913</t>
+          <t>312064</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>268500</t>
+          <t>293878</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>295690</t>
+          <t>326552</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>73,36%</t>
+          <t>72,16%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>69,38%</t>
+          <t>67,95%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>76,4%</t>
+          <t>75,51%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>34135</t>
+          <t>43754</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>25016</t>
+          <t>33406</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>46579</t>
+          <t>55821</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>31085</t>
+          <t>36927</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>23234</t>
+          <t>28278</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>41061</t>
+          <t>48210</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>65220</t>
+          <t>80680</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>53950</t>
+          <t>67312</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>79988</t>
+          <t>98472</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>22,77%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3570,32 +3570,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>15825</t>
+          <t>16049</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>10259</t>
+          <t>10169</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>24932</t>
+          <t>23483</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,32 +3605,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>23397</t>
+          <t>24023</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>16802</t>
+          <t>17309</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>30483</t>
+          <t>31914</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>39222</t>
+          <t>40072</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>30879</t>
+          <t>31401</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>49582</t>
+          <t>51140</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,57%</t>
         </is>
       </c>
     </row>
@@ -3683,32 +3683,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>25299</t>
+          <t>24778</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>17856</t>
+          <t>18121</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>34049</t>
+          <t>34631</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>47984</t>
+          <t>49148</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>39079</t>
+          <t>40397</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>57201</t>
+          <t>58545</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>73284</t>
+          <t>73926</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>61505</t>
+          <t>61796</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>85811</t>
+          <t>86308</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,15%</t>
         </is>
       </c>
     </row>
@@ -3796,32 +3796,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>38252</t>
+          <t>38943</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>29619</t>
+          <t>30325</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>48761</t>
+          <t>49449</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3831,32 +3831,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>43029</t>
+          <t>44860</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>34322</t>
+          <t>36766</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>52093</t>
+          <t>54822</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,32 +3866,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>81281</t>
+          <t>83802</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>68869</t>
+          <t>71700</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>94238</t>
+          <t>97845</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>18,31%</t>
         </is>
       </c>
     </row>
@@ -3909,27 +3909,27 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>190260</t>
+          <t>190938</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>175385</t>
+          <t>176634</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>201696</t>
+          <t>202485</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>70,56%</t>
+          <t>70,53%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>65,05%</t>
+          <t>65,25%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -3944,32 +3944,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>142645</t>
+          <t>145720</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>129668</t>
+          <t>133007</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>154984</t>
+          <t>158329</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>55,49%</t>
+          <t>55,25%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>50,44%</t>
+          <t>50,43%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>60,29%</t>
+          <t>60,03%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,32 +3979,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>332906</t>
+          <t>336657</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>315141</t>
+          <t>317719</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>350367</t>
+          <t>353779</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>63,21%</t>
+          <t>62,99%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>59,45%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>66,52%</t>
+          <t>66,19%</t>
         </is>
       </c>
     </row>
@@ -4022,17 +4022,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4139,32 +4139,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>32504</t>
+          <t>38142</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>23626</t>
+          <t>26598</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>45331</t>
+          <t>52736</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,32 +4174,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>64169</t>
+          <t>81507</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>28358</t>
+          <t>66108</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>89753</t>
+          <t>100386</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>96673</t>
+          <t>119648</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>58984</t>
+          <t>100651</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>119730</t>
+          <t>143876</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>9,65%</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>46101</t>
+          <t>52677</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>34555</t>
+          <t>39953</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>61942</t>
+          <t>68202</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,32 +4287,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>98047</t>
+          <t>117305</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>49901</t>
+          <t>100844</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>135651</t>
+          <t>136272</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>144149</t>
+          <t>169981</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>90593</t>
+          <t>148278</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>177136</t>
+          <t>191113</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,82%</t>
         </is>
       </c>
     </row>
@@ -4365,32 +4365,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>137907</t>
+          <t>164657</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>118234</t>
+          <t>140273</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>160977</t>
+          <t>192572</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,32 +4400,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>368516</t>
+          <t>194905</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>207656</t>
+          <t>173530</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>609789</t>
+          <t>216636</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>71,8%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>506423</t>
+          <t>359562</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>342694</t>
+          <t>324708</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>810989</t>
+          <t>395464</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>55,08%</t>
+          <t>26,53%</t>
         </is>
       </c>
     </row>
@@ -4478,32 +4478,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>406738</t>
+          <t>463130</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>380408</t>
+          <t>432830</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>431924</t>
+          <t>492285</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>65,26%</t>
+          <t>64,45%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>61,04%</t>
+          <t>60,23%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>69,3%</t>
+          <t>68,51%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4513,32 +4513,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>318532</t>
+          <t>378340</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>155902</t>
+          <t>355256</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>430417</t>
+          <t>406085</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>49,0%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>46,01%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>50,68%</t>
+          <t>52,6%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,32 +4548,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>725269</t>
+          <t>841471</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>490966</t>
+          <t>801327</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>853022</t>
+          <t>882025</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>49,25%</t>
+          <t>56,45%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>53,76%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>57,93%</t>
+          <t>59,17%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>623250</t>
+          <t>718605</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>623250</t>
+          <t>718605</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>623250</t>
+          <t>718605</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>1472514</t>
+          <t>1490662</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1472514</t>
+          <t>1490662</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1472514</t>
+          <t>1490662</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4708,32 +4708,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>95768</t>
+          <t>107828</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>43686</t>
+          <t>90211</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>137108</t>
+          <t>126829</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4743,32 +4743,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>133807</t>
+          <t>153811</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>118387</t>
+          <t>137992</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>151482</t>
+          <t>172737</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4778,32 +4778,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>229575</t>
+          <t>261639</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>139023</t>
+          <t>236172</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>278996</t>
+          <t>290774</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,85%</t>
         </is>
       </c>
     </row>
@@ -4821,32 +4821,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>46772</t>
+          <t>51505</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>22463</t>
+          <t>39357</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>69828</t>
+          <t>65120</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4856,32 +4856,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>83691</t>
+          <t>97293</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>69439</t>
+          <t>80008</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>96249</t>
+          <t>112270</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4891,32 +4891,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>130463</t>
+          <t>148797</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>80554</t>
+          <t>129224</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>160653</t>
+          <t>171083</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>10,5%</t>
         </is>
       </c>
     </row>
@@ -4934,32 +4934,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>88858</t>
+          <t>102310</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>36658</t>
+          <t>85071</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>128919</t>
+          <t>122053</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4969,32 +4969,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>112245</t>
+          <t>131370</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>96791</t>
+          <t>113482</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>128382</t>
+          <t>149465</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5004,32 +5004,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>201103</t>
+          <t>233680</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>127288</t>
+          <t>208727</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>246831</t>
+          <t>262133</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>16,09%</t>
         </is>
       </c>
     </row>
@@ -5047,32 +5047,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>697322</t>
+          <t>536429</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>603072</t>
+          <t>509039</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>826048</t>
+          <t>563298</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>75,08%</t>
+          <t>67,22%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>63,78%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>70,58%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5082,32 +5082,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>385649</t>
+          <t>448135</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>362522</t>
+          <t>423914</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>409646</t>
+          <t>475214</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>53,91%</t>
+          <t>53,95%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>50,67%</t>
+          <t>51,04%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>57,26%</t>
+          <t>57,21%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5117,32 +5117,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>1082971</t>
+          <t>984565</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>972753</t>
+          <t>945972</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1296121</t>
+          <t>1023364</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>65,87%</t>
+          <t>60,45%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>59,17%</t>
+          <t>58,08%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>62,83%</t>
         </is>
       </c>
     </row>
@@ -5160,17 +5160,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5195,17 +5195,17 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5230,17 +5230,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5277,32 +5277,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>207989</t>
+          <t>229868</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>164739</t>
+          <t>200258</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>241932</t>
+          <t>257390</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5312,32 +5312,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>331214</t>
+          <t>377184</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>263960</t>
+          <t>349499</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>369815</t>
+          <t>407118</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5347,32 +5347,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>539203</t>
+          <t>607052</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>471457</t>
+          <t>568166</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>596950</t>
+          <t>653772</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>9,0%</t>
         </is>
       </c>
     </row>
@@ -5390,32 +5390,32 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>245807</t>
+          <t>262852</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>193285</t>
+          <t>231205</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>279149</t>
+          <t>295881</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5425,32 +5425,32 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>416710</t>
+          <t>463090</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>342095</t>
+          <t>430619</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>464038</t>
+          <t>498257</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5460,32 +5460,32 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>662517</t>
+          <t>725942</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>585885</t>
+          <t>682668</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>726489</t>
+          <t>772046</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,63%</t>
         </is>
       </c>
     </row>
@@ -5503,32 +5503,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>589067</t>
+          <t>660472</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>455661</t>
+          <t>615675</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>656590</t>
+          <t>709661</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5538,32 +5538,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>993961</t>
+          <t>874292</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>818927</t>
+          <t>832242</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>1552193</t>
+          <t>918950</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5573,32 +5573,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>1583027</t>
+          <t>1534764</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>1375464</t>
+          <t>1473557</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>2165804</t>
+          <t>1606054</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>22,11%</t>
         </is>
       </c>
     </row>
@@ -5616,32 +5616,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>2415925</t>
+          <t>2378487</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>2315878</t>
+          <t>2321435</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>2660483</t>
+          <t>2433625</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>69,85%</t>
+          <t>67,35%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>66,96%</t>
+          <t>65,73%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>68,91%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5651,32 +5651,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>1917047</t>
+          <t>2019033</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>1531210</t>
+          <t>1967762</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>2059356</t>
+          <t>2071888</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>52,39%</t>
+          <t>54,08%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>52,7%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>56,28%</t>
+          <t>55,49%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5686,32 +5686,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>4332971</t>
+          <t>4397520</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>3957080</t>
+          <t>4314385</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>4592467</t>
+          <t>4478098</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>60,88%</t>
+          <t>60,53%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>59,38%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>64,52%</t>
+          <t>61,64%</t>
         </is>
       </c>
     </row>
@@ -5729,17 +5729,17 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>3458787</t>
+          <t>3531680</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>3458787</t>
+          <t>3531680</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>3458787</t>
+          <t>3531680</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5764,17 +5764,17 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>3658932</t>
+          <t>3733598</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>3658932</t>
+          <t>3733598</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>3658932</t>
+          <t>3733598</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5799,17 +5799,17 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>7117719</t>
+          <t>7265279</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>7117719</t>
+          <t>7265279</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>7117719</t>
+          <t>7265279</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
